--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260616.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260616.xlsx
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>778,000</t>
+          <t>1,726,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,726,000</t>
+          <t>778,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>577,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>577,000</t>
+          <t>371,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>371,000</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2,132,107</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,132,107</t>
+          <t>5,015,956</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>202607WVHFN6F</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>5,015,956</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>1,187,076</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>1,187,076</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>327,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>327,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
